--- a/Fischer_Tropsch/Südafrika_FischerTropsch_6_Naphta_Bio_Reaktor_Greenfield/Datenbank.xlsx
+++ b/Fischer_Tropsch/Südafrika_FischerTropsch_6_Naphta_Bio_Reaktor_Greenfield/Datenbank.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Südafrika_6_FischerTropsch_Naphta_Bio_Reaktor_Greenfield\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Südafrika_FischerTropsch_6_Naphta_Bio_Reaktor_Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE3BC04-BB8A-453C-BCAF-172C76D1E26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCC6E8D-6468-4337-92D8-346285AB604D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1633,11 +1633,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2115,7 +2115,7 @@
         <v>302</v>
       </c>
       <c r="E8" s="16">
-        <v>38.99</v>
+        <v>10</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>313</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="41"/>
-      <c r="B82" s="53" t="s">
+      <c r="B82" s="54" t="s">
         <v>376</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -4437,7 +4437,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="41"/>
-      <c r="B83" s="53"/>
+      <c r="B83" s="54"/>
       <c r="C83" s="1" t="s">
         <v>380</v>
       </c>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="53"/>
+      <c r="B84" s="54"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -5297,7 +5297,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="41"/>
-      <c r="B151" s="54" t="s">
+      <c r="B151" s="53" t="s">
         <v>355</v>
       </c>
       <c r="C151" s="1" t="s">
@@ -5312,7 +5312,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="41"/>
-      <c r="B152" s="54"/>
+      <c r="B152" s="53"/>
       <c r="C152" s="1" t="s">
         <v>357</v>
       </c>
@@ -5325,12 +5325,15 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B145:B150"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="A120:A152"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B130:B144"/>
-    <mergeCell ref="B123:B129"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="A47:A78"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B47:B56"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="B34:B46"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="A79:A104"/>
@@ -5342,15 +5345,12 @@
     <mergeCell ref="B111:B113"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="A47:A78"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B47:B56"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B145:B150"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="A120:A152"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B130:B144"/>
+    <mergeCell ref="B123:B129"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
